--- a/www/ig/fhir/ror/StructureDefinition-ror-contact-telecom-usage.xlsx
+++ b/www/ig/fhir/ror/StructureDefinition-ror-contact-telecom-usage.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T09:54:01+00:00</t>
+    <t>2026-04-29T15:35:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -237,7 +237,7 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: Spécification métier vers l'extension ROR ContactTelecomUsaget</t>
+    <t>Mapping: Spécification métier vers l'extension ROR ContactTelecomUsage</t>
   </si>
   <si>
     <t>Mapping: RIM Mapping</t>
@@ -687,7 +687,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="78.8984375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="78.0234375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="24.98046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
